--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N85_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N85_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.44058350723346</v>
+        <v>2.996594819925436</v>
       </c>
       <c r="D2" t="n">
-        <v>19.22582552608988</v>
+        <v>3.124196647989606</v>
       </c>
       <c r="E2" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F2" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.41953427756556</v>
+        <v>2.180674320104404</v>
       </c>
       <c r="D3" t="n">
-        <v>14.67979509250461</v>
+        <v>2.385466702531998</v>
       </c>
       <c r="E3" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F3" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.53275101218224</v>
+        <v>6.099072039479614</v>
       </c>
       <c r="D4" t="n">
-        <v>38.32569293466983</v>
+        <v>6.227925101883848</v>
       </c>
       <c r="E4" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F4" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.28516195041365</v>
+        <v>4.108838816942217</v>
       </c>
       <c r="D5" t="n">
-        <v>23.29987160773739</v>
+        <v>3.786229136257326</v>
       </c>
       <c r="E5" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F5" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.36870597589323</v>
+        <v>6.234914721082649</v>
       </c>
       <c r="D6" t="n">
-        <v>38.09235852212063</v>
+        <v>6.190008259844603</v>
       </c>
       <c r="E6" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F6" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.52543221209078</v>
+        <v>8.697882734464752</v>
       </c>
       <c r="D7" t="n">
-        <v>51.53892821270298</v>
+        <v>8.375075834564234</v>
       </c>
       <c r="E7" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F7" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>48.1836447600317</v>
+        <v>7.829842273505152</v>
       </c>
       <c r="D8" t="n">
-        <v>28.17849850112275</v>
+        <v>4.579006006432447</v>
       </c>
       <c r="E8" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F8" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.34628743799007</v>
+        <v>6.718771708673387</v>
       </c>
       <c r="D9" t="n">
-        <v>41.12501558306898</v>
+        <v>6.682815032248709</v>
       </c>
       <c r="E9" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F9" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>41.37001421004542</v>
+        <v>6.722627309132381</v>
       </c>
       <c r="D10" t="n">
-        <v>40.33142205531305</v>
+        <v>6.553856083988371</v>
       </c>
       <c r="E10" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F10" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>38.66081821416915</v>
+        <v>6.282382959802487</v>
       </c>
       <c r="D11" t="n">
-        <v>38.88180074871215</v>
+        <v>6.318292621665725</v>
       </c>
       <c r="E11" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F11" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.80889021673454</v>
+        <v>4.031444660219362</v>
       </c>
       <c r="D12" t="n">
-        <v>24.27887039097699</v>
+        <v>3.945316438533762</v>
       </c>
       <c r="E12" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F12" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47003702328875</v>
+        <v>5.113881016284423</v>
       </c>
       <c r="D13" t="n">
-        <v>31.75690850435094</v>
+        <v>5.160497631957028</v>
       </c>
       <c r="E13" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F13" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.77468214211362</v>
+        <v>6.463385848093464</v>
       </c>
       <c r="D14" t="n">
-        <v>39.86736050292905</v>
+        <v>6.47844608172597</v>
       </c>
       <c r="E14" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F14" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>39.09833379787629</v>
+        <v>6.353479242154897</v>
       </c>
       <c r="D15" t="n">
-        <v>39.65792531119681</v>
+        <v>6.444412863069482</v>
       </c>
       <c r="E15" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F15" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>17.11448355438414</v>
+        <v>2.781103577587424</v>
       </c>
       <c r="D16" t="n">
-        <v>17.56457205222392</v>
+        <v>2.854242958486386</v>
       </c>
       <c r="E16" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F16" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>19.79682168426842</v>
+        <v>3.216983523693618</v>
       </c>
       <c r="D17" t="n">
-        <v>21.05000571899298</v>
+        <v>3.42062592933636</v>
       </c>
       <c r="E17" t="n">
-        <v>11.47565347543294</v>
+        <v>1.864793689757853</v>
       </c>
       <c r="F17" t="n">
-        <v>10.36770208319418</v>
+        <v>1.684751588519055</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
